--- a/lcr_analyses/clustering/carriers/SEG/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/SEG/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4354,4 +4358,5482 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2713472485768501</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6783216783216783</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07692307692307691</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05594405594405593</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8671328671328671</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03496503496503497</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1958041958041958</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1258741258741259</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6713286713286714</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08466819221967964</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1272727272727273</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9324324324324325</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9041095890410958</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>161</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0430622009569378</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03105590062111801</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3416149068322981</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09937888198757763</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4472049689440994</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1677018633540373</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1490683229813665</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03105590062111801</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.05590062111801242</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01863354037267081</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2957746478873239</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0602409638554217</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>99</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01278574196048043</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03240938545894752</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1570723684210527</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.04653679653679654</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8169856459330144</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.6671052631578948</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.7349498327759196</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.6375</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.06904761904761905</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.118140243902439</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7483870967741936</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1354838709677419</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.006451612903225805</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2967741935483871</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4903225806451613</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.1032258064516129</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2709677419354839</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2713472485768501</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6783216783216783</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07692307692307691</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05594405594405593</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8671328671328671</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03496503496503497</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1958041958041958</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1258741258741259</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6713286713286714</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08466819221967964</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1272727272727273</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9324324324324325</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9041095890410958</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04026845637583892</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.08108108108108104</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2432432432432433</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>158</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04353413537983461</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3417721518987342</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08860759493670886</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4493670886075949</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1708860759493671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1518987341772152</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.05696202531645569</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0189873417721519</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1455696202531646</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6139240506329114</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2943802521008403</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6376262626262625</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.06012048192771085</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8811764705882352</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>35</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01278574196048043</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>72</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03240938545894752</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1570723684210527</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.04653679653679654</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8169856459330144</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.6671052631578948</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.7349498327759196</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.6375</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.06904761904761905</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.118140243902439</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7483870967741936</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.1354838709677419</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.006451612903225805</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2967741935483871</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.4903225806451613</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.1032258064516129</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2709677419354839</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2713472485768501</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6783216783216783</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07692307692307691</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05594405594405593</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8671328671328671</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03496503496503497</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1958041958041958</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1258741258741259</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6713286713286714</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0273037542662116</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09302699803325586</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9321253071253071</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1318840579710144</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.02565789473684211</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.02817460317460317</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.4409302325581396</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0209450069485805</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4606060606060606</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3184121621621622</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4121212121212121</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04026845637583892</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.08108108108108104</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2432432432432433</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>158</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04353413537983461</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3417721518987342</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08860759493670886</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4493670886075949</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1708860759493671</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1518987341772152</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05696202531645569</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0189873417721519</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1455696202531646</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6139240506329114</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2943802521008403</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.6376262626262625</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.06012048192771085</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8811764705882352</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>35</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01278574196048043</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03240938545894752</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.1570723684210527</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.04653679653679654</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8169856459330144</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6671052631578948</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7349498327759196</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.6375</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.06904761904761905</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.118140243902439</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.7483870967741936</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1354838709677419</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.006451612903225805</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2967741935483871</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4903225806451613</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.1032258064516129</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2709677419354839</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2713472485768501</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6783216783216783</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07692307692307691</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05594405594405593</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8671328671328671</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.03496503496503497</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1958041958041958</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1258741258741259</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6713286713286714</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0273037542662116</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09302699803325586</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9321253071253071</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1318840579710144</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.02565789473684211</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.02817460317460317</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.4409302325581396</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0209450069485805</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4606060606060606</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3184121621621622</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4121212121212121</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04026845637583892</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.08108108108108104</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2432432432432433</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04786439665471924</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.04904306220095694</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.6687306501547987</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05213903743315508</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.3312693498452012</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.166267942583732</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>154</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04353413537983461</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03896103896103896</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.03246753246753246</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3506493506493507</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4415584415584415</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1753246753246753</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1558441558441558</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.05844155844155844</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1493506493506493</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6298701298701299</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.297887323943662</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6346375143843499</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.0582579185520362</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4419642857142857</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>33</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01278574196048043</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>72</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03240938545894752</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1570723684210527</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.04653679653679654</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8169856459330144</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.6671052631578948</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.7349498327759196</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.6375</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.06904761904761905</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.118140243902439</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.7483870967741936</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1354838709677419</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.006451612903225805</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.2967741935483871</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.4903225806451613</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1032258064516129</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2709677419354839</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>